--- a/data/trans_orig/P1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -836,57 +836,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -953,47 +953,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1066,57 +1066,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1183,47 +1183,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,57 +1296,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,47 +1413,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1526,57 +1526,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1643,47 +1643,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1756,57 +1756,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1937,7 +1937,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2105,47 +2105,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -2218,57 +2218,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2335,47 +2335,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2448,57 +2448,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2678,57 +2678,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2795,47 +2795,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2908,57 +2908,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3025,47 +3025,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3138,57 +3138,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3308,7 +3308,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3319,7 +3319,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3487,47 +3487,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3600,57 +3600,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3717,47 +3717,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3830,57 +3830,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3947,47 +3947,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4060,57 +4060,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4177,47 +4177,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -4290,57 +4290,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4407,47 +4407,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4520,57 +4520,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4701,7 +4701,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4869,64 +4869,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -4982,57 +4982,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5057,17 +5057,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5099,64 +5099,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>182554</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -5212,57 +5212,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5287,17 +5287,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5329,64 +5329,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>175518</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -5442,57 +5442,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -5677,17 +5677,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5712,17 +5712,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5747,17 +5747,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5789,64 +5789,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>629678</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>761972</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -5902,57 +5902,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5977,17 +5977,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
